--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-keimzahl-einheiten-ucum.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-keimzahl-einheiten-ucum.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Einheiten-ValueSet für die Keimzahlbestimmung (UCUM): koloniebildende Einheiten pro Volumen oder Masse.</t>
+    <t>Einheiten-ValueSet für die Keimzahlbestimmung (UCUM): koloniebildende Einheiten je Volumen, je Masse oder als Anzahl je Probe.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -103,6 +103,12 @@
   </si>
   <si>
     <t>[CFU]/mL</t>
+  </si>
+  <si>
+    <t>[CFU]/g</t>
+  </si>
+  <si>
+    <t>[CFU]</t>
   </si>
   <si>
     <t>[arb'U]/mL</t>
@@ -387,7 +393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -436,16 +442,28 @@
       <c r="A7" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
         <v>36</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-keimzahl-einheiten-ucum.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-keimzahl-einheiten-ucum.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
